--- a/sports_forms/003_school_sports_clinic_enrollment_form--sports_forms.xlsx
+++ b/sports_forms/003_school_sports_clinic_enrollment_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'pay_online',_'value':_'online'}</t>
+          <t>pay_online</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Pay Online', 'value': 'online'}</t>
+          <t>Pay Online</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'pay_offline',_'value':_'offline'}</t>
+          <t>pay_offline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Pay Offline', 'value': 'offline'}</t>
+          <t>Pay Offline</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'school_1',_'value':_'school1'}</t>
+          <t>school_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'School 1', 'value': 'school1'}</t>
+          <t>School 1</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'school_2',_'value':_'school2'}</t>
+          <t>school_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'School 2', 'value': 'school2'}</t>
+          <t>School 2</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'school_1',_'value':_'school1'}</t>
+          <t>school_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'School 1', 'value': 'school1'}</t>
+          <t>School 1</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'school_2',_'value':_'school2'}</t>
+          <t>school_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'School 2', 'value': 'school2'}</t>
+          <t>School 2</t>
         </is>
       </c>
     </row>
